--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{719B9AF0-10EB-4906-9283-238FADCE2F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1998E3FA-7AD4-46D4-9135-1AE32D5E1FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>구분</t>
   </si>
@@ -112,6 +112,12 @@
   <si>
     <t>재고주수</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매율</t>
+  </si>
+  <si>
+    <t>재고주수</t>
   </si>
 </sst>
 </file>
@@ -645,7 +651,7 @@
     <col min="11" max="11" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="33.75" thickBot="1">
+    <row r="1" spans="1:15" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +713,7 @@
         <v>214752.25308737866</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="5">
         <v>214752.25308737866</v>
@@ -725,10 +731,10 @@
         <v>96010.846325011575</v>
       </c>
       <c r="M2" s="5">
-        <v>127385.34165361986</v>
+        <v>141477.51871815659</v>
       </c>
       <c r="N2" s="5">
-        <v>185140.60567139171</v>
+        <v>171048.42860685498</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>22</v>
@@ -776,6 +782,7 @@
         <v>32184.425330851984</v>
       </c>
       <c r="O3" s="7">
+        <f t="shared" ref="O3:O8" si="0">+(J3+M3)/(H3+I3+L3)</f>
         <v>0.56083613388131059</v>
       </c>
     </row>
@@ -817,13 +824,14 @@
         <v>11011.818452380954</v>
       </c>
       <c r="M4" s="10">
-        <v>30474.853982909903</v>
+        <v>42567.031047446617</v>
       </c>
       <c r="N4" s="10">
-        <v>21704.277469471053</v>
+        <v>9612.1004049343392</v>
       </c>
       <c r="O4" s="7">
-        <v>0.65453384923505353</v>
+        <f t="shared" si="0"/>
+        <v>0.84700456707993899</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17.25" thickBot="1">
@@ -858,13 +866,14 @@
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10">
-        <v>30311.959247120481</v>
+        <v>32311.959247120481</v>
       </c>
       <c r="N5" s="10">
-        <v>25994.254752879511</v>
+        <v>23994.254752879511</v>
       </c>
       <c r="O5" s="7">
-        <v>0.64408585128480333</v>
+        <f t="shared" si="0"/>
+        <v>0.67200340115585488</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="17.25" thickBot="1">
@@ -905,6 +914,7 @@
         <v>44642.332835611393</v>
       </c>
       <c r="O6" s="7">
+        <f t="shared" si="0"/>
         <v>0.33949105227762322</v>
       </c>
     </row>
@@ -948,6 +958,7 @@
         <v>11093.355569252424</v>
       </c>
       <c r="O7" s="7">
+        <f t="shared" si="0"/>
         <v>5.2929899680132883E-2</v>
       </c>
     </row>
@@ -989,6 +1000,7 @@
         <v>49521.959713325326</v>
       </c>
       <c r="O8" s="7">
+        <f t="shared" si="0"/>
         <v>0.24568525779359018</v>
       </c>
     </row>
@@ -1012,7 +1024,7 @@
         <v>148512.38437864077</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H9" s="5">
         <v>148512.38437864077</v>
@@ -1030,10 +1042,10 @@
         <v>168731.57696526911</v>
       </c>
       <c r="M9" s="5">
-        <v>150913.12570997101</v>
+        <v>136821.12570997101</v>
       </c>
       <c r="N9" s="5">
-        <v>154256.84725529805</v>
+        <v>168348.84725529805</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>23</v>
@@ -1077,13 +1089,14 @@
         <v>74197.777279589573</v>
       </c>
       <c r="M10" s="10">
-        <v>68666.636385592792</v>
+        <v>63666.636385592792</v>
       </c>
       <c r="N10" s="10">
-        <v>61723.881893996775</v>
+        <v>66723.881893996775</v>
       </c>
       <c r="O10" s="12">
-        <v>37.004943638780091</v>
+        <f>+N10/(M10+J10)*52</f>
+        <v>42.449637578796874</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="17.25" thickBot="1">
@@ -1124,13 +1137,14 @@
         <v>74413.471821727158</v>
       </c>
       <c r="M11" s="10">
-        <v>59157.792212302724</v>
+        <v>57065.792212302724</v>
       </c>
       <c r="N11" s="10">
-        <v>73497.483609424424</v>
+        <v>75589.483609424424</v>
       </c>
       <c r="O11" s="12">
-        <v>51.000587990866201</v>
+        <f>+N11/(M11+J11)*52</f>
+        <v>53.958581280084346</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="17.25" thickBot="1">
@@ -1171,13 +1185,14 @@
         <v>17557.526911571415</v>
       </c>
       <c r="M12" s="10">
-        <v>21178.157019052589</v>
+        <v>14178.157019052589</v>
       </c>
       <c r="N12" s="10">
-        <v>15023.130892518828</v>
+        <v>22023.130892518828</v>
       </c>
       <c r="O12" s="12">
-        <v>31.197408743934133</v>
+        <f>+N12/(M12+J12)*52</f>
+        <v>63.479087533584227</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="17.25" thickBot="1">
@@ -1224,6 +1239,7 @@
         <v>4012.350859358045</v>
       </c>
       <c r="O13" s="12">
+        <f>+N13/(M13+J13)*52</f>
         <v>43.011843754930453</v>
       </c>
     </row>
@@ -1263,10 +1279,10 @@
         <v>264742.42329028068</v>
       </c>
       <c r="M14" s="5">
-        <v>278298.46736359084</v>
+        <v>278298.64442812756</v>
       </c>
       <c r="N14" s="5">
-        <v>339397.45292668976</v>
+        <v>339397.27586215304</v>
       </c>
     </row>
   </sheetData>

--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1998E3FA-7AD4-46D4-9135-1AE32D5E1FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48427C41-EC9D-4350-AC2D-B5184814ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -731,10 +731,10 @@
         <v>96010.846325011575</v>
       </c>
       <c r="M2" s="5">
-        <v>141477.51871815659</v>
+        <v>155477.51871815659</v>
       </c>
       <c r="N2" s="5">
-        <v>171048.42860685498</v>
+        <v>157048.42860685498</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>22</v>
@@ -866,14 +866,14 @@
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10">
-        <v>32311.959247120481</v>
+        <v>39311.959247120481</v>
       </c>
       <c r="N5" s="10">
-        <v>23994.254752879511</v>
+        <v>16994.254752879511</v>
       </c>
       <c r="O5" s="7">
         <f t="shared" si="0"/>
-        <v>0.67200340115585488</v>
+        <v>0.7697148257045352</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="17.25" thickBot="1">
@@ -908,14 +908,14 @@
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10">
-        <v>15953.460164388609</v>
+        <v>22953.460164388609</v>
       </c>
       <c r="N6" s="10">
-        <v>44642.332835611393</v>
+        <v>37642.332835611393</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" si="0"/>
-        <v>0.33949105227762322</v>
+        <v>0.44183852467985868</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="17.25" thickBot="1">
@@ -1042,10 +1042,10 @@
         <v>168731.57696526911</v>
       </c>
       <c r="M9" s="5">
-        <v>136821.12570997101</v>
+        <v>158013.12570997101</v>
       </c>
       <c r="N9" s="5">
-        <v>168348.84725529805</v>
+        <v>147156.84725529805</v>
       </c>
       <c r="O9" s="12" t="s">
         <v>23</v>
@@ -1089,14 +1089,14 @@
         <v>74197.777279589573</v>
       </c>
       <c r="M10" s="10">
-        <v>63666.636385592792</v>
+        <v>68666.636385592792</v>
       </c>
       <c r="N10" s="10">
-        <v>66723.881893996775</v>
+        <v>61723.881893996775</v>
       </c>
       <c r="O10" s="12">
         <f>+N10/(M10+J10)*52</f>
-        <v>42.449637578796874</v>
+        <v>37.004943638780091</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="17.25" thickBot="1">
@@ -1137,14 +1137,14 @@
         <v>74413.471821727158</v>
       </c>
       <c r="M11" s="10">
-        <v>57065.792212302724</v>
+        <v>72157.792212302724</v>
       </c>
       <c r="N11" s="10">
-        <v>75589.483609424424</v>
+        <v>60497.483609424424</v>
       </c>
       <c r="O11" s="12">
         <f>+N11/(M11+J11)*52</f>
-        <v>53.958581280084346</v>
+        <v>35.773820269944629</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="17.25" thickBot="1">
@@ -1185,14 +1185,14 @@
         <v>17557.526911571415</v>
       </c>
       <c r="M12" s="10">
-        <v>14178.157019052589</v>
+        <v>15178.157019052589</v>
       </c>
       <c r="N12" s="10">
-        <v>22023.130892518828</v>
+        <v>21023.130892518828</v>
       </c>
       <c r="O12" s="12">
         <f>+N12/(M12+J12)*52</f>
-        <v>63.479087533584227</v>
+        <v>57.414210461652971</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="17.25" thickBot="1">
@@ -1233,14 +1233,14 @@
         <v>2562.8009523809528</v>
       </c>
       <c r="M13" s="10">
-        <v>1910.5400930229075</v>
+        <v>2010.5400930229075</v>
       </c>
       <c r="N13" s="10">
-        <v>4012.350859358045</v>
+        <v>3912.350859358045</v>
       </c>
       <c r="O13" s="12">
         <f>+N13/(M13+J13)*52</f>
-        <v>43.011843754930453</v>
+        <v>41.092726270792006</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="17.25" thickBot="1">
@@ -1279,10 +1279,10 @@
         <v>264742.42329028068</v>
       </c>
       <c r="M14" s="5">
-        <v>278298.64442812756</v>
+        <v>313490.64442812756</v>
       </c>
       <c r="N14" s="5">
-        <v>339397.27586215304</v>
+        <v>304205.27586215304</v>
       </c>
     </row>
   </sheetData>

--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48427C41-EC9D-4350-AC2D-B5184814ED5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4727C-153D-4A2E-84FD-542AD823EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -98,14 +98,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>판매가능</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>26년 2월말</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>판매율</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -118,6 +110,12 @@
   </si>
   <si>
     <t>재고주수</t>
+  </si>
+  <si>
+    <t>판매가능</t>
+  </si>
+  <si>
+    <t>26년 2월말</t>
   </si>
 </sst>
 </file>
@@ -662,7 +660,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -681,7 +679,7 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>2</v>
@@ -713,13 +711,13 @@
         <v>214752.25308737866</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="5">
-        <v>214752.25308737866</v>
+        <v>203512.30156310683</v>
       </c>
       <c r="I2" s="5">
-        <v>40574.291046728154</v>
+        <v>61814.242571000002</v>
       </c>
       <c r="J2" s="5">
         <v>40414.686814000001</v>
@@ -731,13 +729,13 @@
         <v>96010.846325011575</v>
       </c>
       <c r="M2" s="5">
-        <v>155477.51871815659</v>
+        <v>149896.33510990415</v>
       </c>
       <c r="N2" s="5">
-        <v>157048.42860685498</v>
+        <v>162629.61221510742</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="17.25" thickBot="1">
@@ -808,11 +806,9 @@
       <c r="G4" s="11">
         <v>0.58201228178707043</v>
       </c>
-      <c r="H4" s="9">
-        <v>11239.951524271846</v>
-      </c>
+      <c r="H4" s="9"/>
       <c r="I4" s="9">
-        <v>40574.291046728154</v>
+        <v>61814.242571000002</v>
       </c>
       <c r="J4" s="9">
         <v>10646.929570999999</v>
@@ -824,14 +820,14 @@
         <v>11011.818452380954</v>
       </c>
       <c r="M4" s="10">
-        <v>42567.031047446617</v>
+        <v>44985.847439194178</v>
       </c>
       <c r="N4" s="10">
-        <v>9612.1004049343392</v>
+        <v>7193.2840131867779</v>
       </c>
       <c r="O4" s="7">
         <f t="shared" si="0"/>
-        <v>0.84700456707993899</v>
+        <v>0.76391303097298047</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17.25" thickBot="1">
@@ -866,14 +862,14 @@
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10">
-        <v>39311.959247120481</v>
+        <v>34311.959247120481</v>
       </c>
       <c r="N5" s="10">
-        <v>16994.254752879511</v>
+        <v>21994.254752879511</v>
       </c>
       <c r="O5" s="7">
         <f t="shared" si="0"/>
-        <v>0.7697148257045352</v>
+        <v>0.69992095102690632</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="17.25" thickBot="1">
@@ -908,14 +904,14 @@
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10">
-        <v>22953.460164388609</v>
+        <v>19953.460164388609</v>
       </c>
       <c r="N6" s="10">
-        <v>37642.332835611393</v>
+        <v>40642.332835611393</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" si="0"/>
-        <v>0.44183852467985868</v>
+        <v>0.39797532222175774</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="17.25" thickBot="1">
@@ -1024,7 +1020,7 @@
         <v>148512.38437864077</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H9" s="5">
         <v>148512.38437864077</v>
@@ -1039,16 +1035,16 @@
         <v>136438.39599999998</v>
       </c>
       <c r="L9" s="5">
-        <v>168731.57696526911</v>
+        <v>126612.37997057514</v>
       </c>
       <c r="M9" s="5">
-        <v>158013.12570997101</v>
+        <v>129013.12570997102</v>
       </c>
       <c r="N9" s="5">
-        <v>147156.84725529805</v>
+        <v>134037.6502606041</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="17.25" thickBot="1">
@@ -1086,17 +1082,17 @@
         <v>56192.741000000002</v>
       </c>
       <c r="L10" s="9">
-        <v>74197.777279589573</v>
+        <v>56731.54785750981</v>
       </c>
       <c r="M10" s="10">
-        <v>68666.636385592792</v>
+        <v>45666.636385592792</v>
       </c>
       <c r="N10" s="10">
-        <v>61723.881893996775</v>
+        <v>67257.652471917027</v>
       </c>
       <c r="O10" s="12">
         <f>+N10/(M10+J10)*52</f>
-        <v>37.004943638780091</v>
+        <v>54.873635052788899</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="17.25" thickBot="1">
@@ -1134,17 +1130,17 @@
         <v>58241.803999999996</v>
       </c>
       <c r="L11" s="9">
-        <v>74413.471821727158</v>
+        <v>53878.318068063025</v>
       </c>
       <c r="M11" s="10">
-        <v>72157.792212302724</v>
+        <v>67157.792212302724</v>
       </c>
       <c r="N11" s="10">
-        <v>60497.483609424424</v>
+        <v>44962.329855760298</v>
       </c>
       <c r="O11" s="12">
         <f>+N11/(M11+J11)*52</f>
-        <v>35.773820269944629</v>
+        <v>28.190314346782486</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="17.25" thickBot="1">
@@ -1182,17 +1178,17 @@
         <v>18643.760999999999</v>
       </c>
       <c r="L12" s="9">
-        <v>17557.526911571415</v>
+        <v>13439.713092621341</v>
       </c>
       <c r="M12" s="10">
-        <v>15178.157019052589</v>
+        <v>14178.157019052589</v>
       </c>
       <c r="N12" s="10">
-        <v>21023.130892518828</v>
+        <v>17905.317073568753</v>
       </c>
       <c r="O12" s="12">
         <f>+N12/(M12+J12)*52</f>
-        <v>57.414210461652971</v>
+        <v>51.609972958738311</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="17.25" thickBot="1">
@@ -1264,10 +1260,10 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>363264.63746601943</v>
+        <v>352024.68594174762</v>
       </c>
       <c r="I14" s="5">
-        <v>69151.852415087371</v>
+        <v>90391.803939359219</v>
       </c>
       <c r="J14" s="5">
         <v>81066.236560999998</v>
@@ -1276,13 +1272,13 @@
         <v>352953.49699999997</v>
       </c>
       <c r="L14" s="5">
-        <v>264742.42329028068</v>
+        <v>222623.22629558673</v>
       </c>
       <c r="M14" s="5">
-        <v>313490.64442812756</v>
+        <v>278909.46081987518</v>
       </c>
       <c r="N14" s="5">
-        <v>304205.27586215304</v>
+        <v>296667.26247571153</v>
       </c>
     </row>
   </sheetData>

--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC4727C-153D-4A2E-84FD-542AD823EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63577E4F-7A8C-4DB7-A417-0EE05C9C0830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -717,7 +717,7 @@
         <v>203512.30156310683</v>
       </c>
       <c r="I2" s="5">
-        <v>61814.242571000002</v>
+        <v>51814.242571000002</v>
       </c>
       <c r="J2" s="5">
         <v>40414.686814000001</v>
@@ -726,13 +726,13 @@
         <v>216515.101</v>
       </c>
       <c r="L2" s="5">
-        <v>96010.846325011575</v>
+        <v>106010.84632501157</v>
       </c>
       <c r="M2" s="5">
         <v>149896.33510990415</v>
       </c>
       <c r="N2" s="5">
-        <v>162629.61221510742</v>
+        <v>172629.61221510742</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>20</v>
@@ -808,7 +808,7 @@
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9">
-        <v>61814.242571000002</v>
+        <v>51814.242571000002</v>
       </c>
       <c r="J4" s="9">
         <v>10646.929570999999</v>
@@ -817,13 +817,13 @@
         <v>41167.313000000002</v>
       </c>
       <c r="L4" s="9">
-        <v>11011.818452380954</v>
+        <v>21011.818452380954</v>
       </c>
       <c r="M4" s="10">
         <v>44985.847439194178</v>
       </c>
       <c r="N4" s="10">
-        <v>7193.2840131867779</v>
+        <v>17193.284013186778</v>
       </c>
       <c r="O4" s="7">
         <f t="shared" si="0"/>
@@ -1263,7 +1263,7 @@
         <v>352024.68594174762</v>
       </c>
       <c r="I14" s="5">
-        <v>90391.803939359219</v>
+        <v>80391.803939359219</v>
       </c>
       <c r="J14" s="5">
         <v>81066.236560999998</v>
@@ -1272,13 +1272,13 @@
         <v>352953.49699999997</v>
       </c>
       <c r="L14" s="5">
-        <v>222623.22629558673</v>
+        <v>232623.22629558673</v>
       </c>
       <c r="M14" s="5">
         <v>278909.46081987518</v>
       </c>
       <c r="N14" s="5">
-        <v>296667.26247571153</v>
+        <v>306667.26247571153</v>
       </c>
     </row>
   </sheetData>

--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63577E4F-7A8C-4DB7-A417-0EE05C9C0830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEAB571-A231-4111-AA96-E9E2E563A546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -41,46 +41,19 @@
     <t>구분</t>
   </si>
   <si>
-    <t>25년 기초</t>
-  </si>
-  <si>
     <t>입고</t>
   </si>
   <si>
     <t>판매</t>
   </si>
   <si>
-    <t>25년 기말</t>
-  </si>
-  <si>
-    <t>26년 기초</t>
-  </si>
-  <si>
-    <t>26년 기말</t>
-  </si>
-  <si>
     <t>의류합계</t>
   </si>
   <si>
-    <t>당년F</t>
-  </si>
-  <si>
-    <t>당년S</t>
-  </si>
-  <si>
-    <t>1년차</t>
-  </si>
-  <si>
-    <t>2년차</t>
-  </si>
-  <si>
     <t>차기시즌</t>
   </si>
   <si>
     <t>과시즌</t>
-  </si>
-  <si>
-    <t>ACC합계</t>
   </si>
   <si>
     <t>신발</t>
@@ -115,7 +88,248 @@
     <t>판매가능</t>
   </si>
   <si>
-    <t>26년 2월말</t>
+    <r>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기초</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기말</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기초</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>월말</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF334155"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기말</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>당년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF475569"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>당년</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF475569"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF475569"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF475569"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년차</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ACC</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0F172A"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>합계</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -126,7 +340,7 @@
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +401,28 @@
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF334155"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F172A"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF475569"/>
+      <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -263,7 +499,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -307,6 +543,15 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -650,115 +895,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="N1" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A2" s="4" t="s">
-        <v>7</v>
+      <c r="A2" s="16" t="s">
+        <v>3</v>
       </c>
       <c r="B2" s="5">
-        <v>217454</v>
+        <v>211006</v>
       </c>
       <c r="C2" s="5">
-        <v>161427.74374757282</v>
+        <v>167876</v>
       </c>
       <c r="D2" s="5">
-        <v>378881.74374757282</v>
+        <v>378882</v>
       </c>
       <c r="E2" s="5">
-        <v>165266.46206174759</v>
+        <v>165266</v>
       </c>
       <c r="F2" s="5">
-        <v>214752.25308737866</v>
+        <v>214752</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H2" s="5">
-        <v>203512.30156310683</v>
+        <v>203512</v>
       </c>
       <c r="I2" s="5">
-        <v>51814.242571000002</v>
+        <v>51814</v>
       </c>
       <c r="J2" s="5">
-        <v>40414.686814000001</v>
+        <v>40415</v>
       </c>
       <c r="K2" s="5">
-        <v>216515.101</v>
+        <v>216515</v>
       </c>
       <c r="L2" s="5">
-        <v>106010.84632501157</v>
+        <v>106011</v>
       </c>
       <c r="M2" s="5">
-        <v>149896.33510990415</v>
+        <v>149896</v>
       </c>
       <c r="N2" s="5">
-        <v>172629.61221510742</v>
+        <v>172630</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
+      <c r="A3" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="9">
         <v>0</v>
       </c>
       <c r="C3" s="9">
-        <v>73043.318019417478</v>
+        <v>73043</v>
       </c>
       <c r="D3" s="9">
-        <v>73043.318019417478</v>
+        <v>73043</v>
       </c>
       <c r="E3" s="10">
-        <v>36146.54977669903</v>
+        <v>36147</v>
       </c>
       <c r="F3" s="9">
-        <v>36896.768242718448</v>
+        <v>36897</v>
       </c>
       <c r="G3" s="11">
-        <v>0.4948645647106284</v>
+        <v>0.49</v>
       </c>
       <c r="H3" s="9">
         <v>0</v>
@@ -771,68 +1016,66 @@
         <v>0</v>
       </c>
       <c r="L3" s="9">
-        <v>73285.686309523808</v>
+        <v>73286</v>
       </c>
       <c r="M3" s="10">
-        <v>41101.260978671824</v>
+        <v>41101</v>
       </c>
       <c r="N3" s="10">
-        <v>32184.425330851984</v>
+        <v>32184</v>
       </c>
       <c r="O3" s="7">
         <f t="shared" ref="O3:O8" si="0">+(J3+M3)/(H3+I3+L3)</f>
-        <v>0.56083613388131059</v>
+        <v>0.56083017220205766</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A4" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="9">
-        <v>6448</v>
-      </c>
+      <c r="A4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9"/>
       <c r="C4" s="9">
-        <v>76671.084165048553</v>
+        <v>83119</v>
       </c>
       <c r="D4" s="9">
-        <v>83119.084165048553</v>
+        <v>83119</v>
       </c>
       <c r="E4" s="10">
-        <v>48376.327834951466</v>
+        <v>48376</v>
       </c>
       <c r="F4" s="9">
-        <v>34742.756330097087</v>
+        <v>34743</v>
       </c>
       <c r="G4" s="11">
-        <v>0.58201228178707043</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9">
-        <v>51814.242571000002</v>
+        <v>51814</v>
       </c>
       <c r="J4" s="9">
-        <v>10646.929570999999</v>
+        <v>10647</v>
       </c>
       <c r="K4" s="9">
-        <v>41167.313000000002</v>
+        <v>41167</v>
       </c>
       <c r="L4" s="9">
-        <v>21011.818452380954</v>
+        <v>21012</v>
       </c>
       <c r="M4" s="10">
-        <v>44985.847439194178</v>
+        <v>44986</v>
       </c>
       <c r="N4" s="10">
-        <v>17193.284013186778</v>
+        <v>17193</v>
       </c>
       <c r="O4" s="7">
         <f t="shared" si="0"/>
-        <v>0.76391303097298047</v>
+        <v>0.76391673303490515</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17.25" thickBot="1">
       <c r="A5" s="8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B5" s="9">
         <v>116967</v>
@@ -842,39 +1085,39 @@
         <v>116967</v>
       </c>
       <c r="E5" s="10">
-        <v>50041.120450097078</v>
+        <v>50041</v>
       </c>
       <c r="F5" s="9">
-        <v>68394.458951456312</v>
+        <v>68394</v>
       </c>
       <c r="G5" s="11">
-        <v>0.42782255208817083</v>
+        <v>0.43</v>
       </c>
       <c r="H5" s="9">
-        <v>71639.524572815542</v>
+        <v>71640</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9">
-        <v>15830.044922999999</v>
+        <v>15830</v>
       </c>
       <c r="K5" s="9">
-        <v>56306.213999999993</v>
+        <v>56306</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="10">
-        <v>34311.959247120481</v>
+        <v>34312</v>
       </c>
       <c r="N5" s="10">
-        <v>21994.254752879511</v>
+        <v>21994</v>
       </c>
       <c r="O5" s="7">
         <f t="shared" si="0"/>
-        <v>0.69992095102690632</v>
+        <v>0.69991624790619766</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="17.25" thickBot="1">
       <c r="A6" s="8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B6" s="9">
         <v>72725</v>
@@ -884,57 +1127,57 @@
         <v>72725</v>
       </c>
       <c r="E6" s="10">
-        <v>25635.297582524272</v>
+        <v>25635</v>
       </c>
       <c r="F6" s="9">
-        <v>47535.347970873787</v>
+        <v>47535</v>
       </c>
       <c r="G6" s="11">
-        <v>0.35249635727087347</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="9">
-        <v>68394.458951456312</v>
+        <v>68394</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9">
-        <v>7265.8466750000007</v>
+        <v>7266</v>
       </c>
       <c r="K6" s="9">
-        <v>60595.793000000005</v>
+        <v>60596</v>
       </c>
       <c r="L6" s="9"/>
       <c r="M6" s="10">
-        <v>19953.460164388609</v>
+        <v>19953</v>
       </c>
       <c r="N6" s="10">
-        <v>40642.332835611393</v>
+        <v>40642</v>
       </c>
       <c r="O6" s="7">
         <f t="shared" si="0"/>
-        <v>0.39797532222175774</v>
+        <v>0.39797350644793406</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A7" s="8" t="s">
-        <v>12</v>
+      <c r="A7" s="17" t="s">
+        <v>4</v>
       </c>
       <c r="B7" s="9">
         <v>0</v>
       </c>
       <c r="C7" s="9">
-        <v>11713.341563106798</v>
+        <v>11713</v>
       </c>
       <c r="D7" s="9">
-        <v>11713.341563106798</v>
+        <v>11713</v>
       </c>
       <c r="E7" s="10">
-        <v>473.3900388349515</v>
+        <v>473</v>
       </c>
       <c r="F7" s="9">
-        <v>11239.951524271846</v>
+        <v>11240</v>
       </c>
       <c r="G7" s="11">
-        <v>4.0414602125662891E-2</v>
+        <v>0.04</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -945,22 +1188,22 @@
         <v>0</v>
       </c>
       <c r="L7" s="9">
-        <v>11713.341563106798</v>
+        <v>11713</v>
       </c>
       <c r="M7" s="10">
-        <v>619.98599385437376</v>
+        <v>620</v>
       </c>
       <c r="N7" s="10">
-        <v>11093.355569252424</v>
+        <v>11093</v>
       </c>
       <c r="O7" s="7">
         <f t="shared" si="0"/>
-        <v>5.2929899680132883E-2</v>
+        <v>5.2932638948177242E-2</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A8" s="8" t="s">
-        <v>13</v>
+      <c r="A8" s="17" t="s">
+        <v>5</v>
       </c>
       <c r="B8" s="9">
         <v>21314</v>
@@ -970,315 +1213,315 @@
         <v>21314</v>
       </c>
       <c r="E8" s="10">
-        <v>4593.7763786407768</v>
+        <v>4594</v>
       </c>
       <c r="F8" s="9">
-        <v>15942.970067961163</v>
+        <v>15943</v>
       </c>
       <c r="G8" s="11">
-        <v>0.21552859053395781</v>
+        <v>0.22</v>
       </c>
       <c r="H8" s="9">
-        <v>63478.31803883495</v>
+        <v>63478</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9">
-        <v>6671.8656450000008</v>
+        <v>6672</v>
       </c>
       <c r="K8" s="9">
-        <v>58445.780999999995</v>
+        <v>58446</v>
       </c>
       <c r="L8" s="9"/>
       <c r="M8" s="10">
-        <v>8923.821286674669</v>
+        <v>8924</v>
       </c>
       <c r="N8" s="10">
-        <v>49521.959713325326</v>
+        <v>49522</v>
       </c>
       <c r="O8" s="7">
         <f t="shared" si="0"/>
-        <v>0.24568525779359018</v>
+        <v>0.24569142064967389</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="17.25" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5">
         <v>168561</v>
       </c>
       <c r="C9" s="5">
-        <v>131295.24416912621</v>
+        <v>131295</v>
       </c>
       <c r="D9" s="5">
-        <v>299856.24416912621</v>
+        <v>299856</v>
       </c>
       <c r="E9" s="5">
-        <v>151343.85979048547</v>
+        <v>151344</v>
       </c>
       <c r="F9" s="5">
-        <v>148512.38437864077</v>
+        <v>148512</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H9" s="5">
-        <v>148512.38437864077</v>
+        <v>148512</v>
       </c>
       <c r="I9" s="5">
-        <v>28577.56136835922</v>
+        <v>28578</v>
       </c>
       <c r="J9" s="5">
-        <v>40651.549746999997</v>
+        <v>40652</v>
       </c>
       <c r="K9" s="5">
-        <v>136438.39599999998</v>
+        <v>136438</v>
       </c>
       <c r="L9" s="5">
-        <v>126612.37997057514</v>
+        <v>126612</v>
       </c>
       <c r="M9" s="5">
-        <v>129013.12570997102</v>
+        <v>129013</v>
       </c>
       <c r="N9" s="5">
-        <v>134037.6502606041</v>
+        <v>134038</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A10" s="8" t="s">
-        <v>15</v>
+      <c r="A10" s="17" t="s">
+        <v>6</v>
       </c>
       <c r="B10" s="9">
         <v>68304</v>
       </c>
       <c r="C10" s="9">
-        <v>61029.624637961228</v>
+        <v>61030</v>
       </c>
       <c r="D10" s="13">
-        <v>129333.62463796123</v>
+        <v>129334</v>
       </c>
       <c r="E10" s="14">
-        <v>68524.55213310683</v>
+        <v>68525</v>
       </c>
       <c r="F10" s="9">
-        <v>60809.072504854397</v>
+        <v>60809</v>
       </c>
       <c r="G10" s="5">
-        <v>46.145092113994437</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9">
-        <v>60809.072504854397</v>
+        <v>60809</v>
       </c>
       <c r="I10" s="9">
-        <v>13452.520476145597</v>
+        <v>13453</v>
       </c>
       <c r="J10" s="9">
-        <v>18068.851981</v>
+        <v>18069</v>
       </c>
       <c r="K10" s="9">
-        <v>56192.741000000002</v>
+        <v>56193</v>
       </c>
       <c r="L10" s="9">
-        <v>56731.54785750981</v>
+        <v>56732</v>
       </c>
       <c r="M10" s="10">
-        <v>45666.636385592792</v>
+        <v>45667</v>
       </c>
       <c r="N10" s="10">
-        <v>67257.652471917027</v>
+        <v>67258</v>
       </c>
       <c r="O10" s="12">
         <f>+N10/(M10+J10)*52</f>
-        <v>54.873635052788899</v>
+        <v>54.873478097150745</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A11" s="8" t="s">
-        <v>16</v>
+      <c r="A11" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="B11" s="9">
         <v>66873</v>
       </c>
       <c r="C11" s="9">
-        <v>55921.364929223259</v>
+        <v>55921</v>
       </c>
       <c r="D11" s="9">
-        <v>122794.36492922326</v>
+        <v>122794</v>
       </c>
       <c r="E11" s="10">
-        <v>59203.857977766973</v>
+        <v>59204</v>
       </c>
       <c r="F11" s="9">
-        <v>63590.506951456278</v>
+        <v>63591</v>
       </c>
       <c r="G11" s="5">
-        <v>55.852886525021823</v>
+        <v>56</v>
       </c>
       <c r="H11" s="9">
-        <v>63590.506951456278</v>
+        <v>63591</v>
       </c>
       <c r="I11" s="9">
-        <v>10431.251600543721</v>
+        <v>10431</v>
       </c>
       <c r="J11" s="9">
-        <v>15779.954551999999</v>
+        <v>15780</v>
       </c>
       <c r="K11" s="9">
-        <v>58241.803999999996</v>
+        <v>58242</v>
       </c>
       <c r="L11" s="9">
-        <v>53878.318068063025</v>
+        <v>53878</v>
       </c>
       <c r="M11" s="10">
-        <v>67157.792212302724</v>
+        <v>67158</v>
       </c>
       <c r="N11" s="10">
-        <v>44962.329855760298</v>
+        <v>44962</v>
       </c>
       <c r="O11" s="12">
         <f>+N11/(M11+J11)*52</f>
-        <v>28.190314346782486</v>
+        <v>28.190021461814851</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A12" s="8" t="s">
-        <v>17</v>
+      <c r="A12" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="B12" s="9">
         <v>25865</v>
       </c>
       <c r="C12" s="9">
-        <v>13890.26142718445</v>
+        <v>13890</v>
       </c>
       <c r="D12" s="9">
-        <v>39755.26142718445</v>
+        <v>39755</v>
       </c>
       <c r="E12" s="10">
-        <v>19783.113805825225</v>
+        <v>19783</v>
       </c>
       <c r="F12" s="9">
-        <v>19972.147621359225</v>
+        <v>19972</v>
       </c>
       <c r="G12" s="5">
-        <v>52.496876199785774</v>
+        <v>52</v>
       </c>
       <c r="H12" s="9">
-        <v>19972.147621359225</v>
+        <v>19972</v>
       </c>
       <c r="I12" s="9">
-        <v>2534.0875486407749</v>
+        <v>2534</v>
       </c>
       <c r="J12" s="9">
-        <v>3862.47417</v>
+        <v>3862</v>
       </c>
       <c r="K12" s="9">
-        <v>18643.760999999999</v>
+        <v>18644</v>
       </c>
       <c r="L12" s="9">
-        <v>13439.713092621341</v>
+        <v>13440</v>
       </c>
       <c r="M12" s="10">
-        <v>14178.157019052589</v>
+        <v>14178</v>
       </c>
       <c r="N12" s="10">
-        <v>17905.317073568753</v>
+        <v>17905</v>
       </c>
       <c r="O12" s="12">
         <f>+N12/(M12+J12)*52</f>
-        <v>51.609972958738311</v>
+        <v>51.610864745011085</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="17.25" thickBot="1">
-      <c r="A13" s="8" t="s">
-        <v>18</v>
+      <c r="A13" s="17" t="s">
+        <v>9</v>
       </c>
       <c r="B13" s="9">
         <v>7519</v>
       </c>
       <c r="C13" s="9">
-        <v>453.99317475728094</v>
+        <v>454</v>
       </c>
       <c r="D13" s="9">
-        <v>7972.9931747572809</v>
+        <v>7973</v>
       </c>
       <c r="E13" s="10">
-        <v>3832.3358737864078</v>
+        <v>3832</v>
       </c>
       <c r="F13" s="9">
-        <v>4140.6573009708736</v>
+        <v>4141</v>
       </c>
       <c r="G13" s="5">
-        <v>56.18353577077044</v>
+        <v>56</v>
       </c>
       <c r="H13" s="9">
-        <v>4140.6573009708736</v>
+        <v>4141</v>
       </c>
       <c r="I13" s="9">
-        <v>2159.7017430291271</v>
+        <v>2160</v>
       </c>
       <c r="J13" s="9">
-        <v>2940.2690440000001</v>
+        <v>2940</v>
       </c>
       <c r="K13" s="9">
-        <v>3360.09</v>
+        <v>3360</v>
       </c>
       <c r="L13" s="9">
-        <v>2562.8009523809528</v>
+        <v>2563</v>
       </c>
       <c r="M13" s="10">
-        <v>2010.5400930229075</v>
+        <v>2011</v>
       </c>
       <c r="N13" s="10">
-        <v>3912.350859358045</v>
+        <v>3912</v>
       </c>
       <c r="O13" s="12">
         <f>+N13/(M13+J13)*52</f>
-        <v>41.092726270792006</v>
+        <v>41.087457079377906</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="17.25" thickBot="1">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>386015</v>
+        <v>379567</v>
       </c>
       <c r="C14" s="5">
-        <v>292722.98791669903</v>
+        <v>299171</v>
       </c>
       <c r="D14" s="5">
-        <v>678737.98791669903</v>
+        <v>678738</v>
       </c>
       <c r="E14" s="5">
-        <v>316610.32185223303</v>
+        <v>316610</v>
       </c>
       <c r="F14" s="5">
-        <v>363264.63746601943</v>
+        <v>363265</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>352024.68594174762</v>
+        <v>352025</v>
       </c>
       <c r="I14" s="5">
-        <v>80391.803939359219</v>
+        <v>80392</v>
       </c>
       <c r="J14" s="5">
-        <v>81066.236560999998</v>
+        <v>81066</v>
       </c>
       <c r="K14" s="5">
-        <v>352953.49699999997</v>
+        <v>352953</v>
       </c>
       <c r="L14" s="5">
-        <v>232623.22629558673</v>
+        <v>232623</v>
       </c>
       <c r="M14" s="5">
-        <v>278909.46081987518</v>
+        <v>278909</v>
       </c>
       <c r="N14" s="5">
-        <v>306667.26247571153</v>
+        <v>306667</v>
       </c>
     </row>
   </sheetData>

--- a/2602_inventory.xlsx
+++ b/2602_inventory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cursor_work_space\Working Capital Dashboard\cashflow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEAB571-A231-4111-AA96-E9E2E563A546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAA4D41-E09C-40F7-A548-B07B0FE96772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="26430" windowHeight="16440" xr2:uid="{D593AF19-A322-4513-BC5A-A55E0694C254}"/>
   </bookViews>
@@ -259,34 +259,6 @@
   </si>
   <si>
     <r>
-      <t>당년</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF475569"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>당년</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF475569"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>1</t>
     </r>
     <r>
@@ -330,6 +302,12 @@
       </rPr>
       <t>합계</t>
     </r>
+  </si>
+  <si>
+    <t>당년F</t>
+  </si>
+  <si>
+    <t>당년S</t>
   </si>
 </sst>
 </file>
@@ -971,13 +949,13 @@
         <v>216515</v>
       </c>
       <c r="L2" s="5">
-        <v>106011</v>
+        <v>112011</v>
       </c>
       <c r="M2" s="5">
         <v>149896</v>
       </c>
       <c r="N2" s="5">
-        <v>172630</v>
+        <v>178630</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>11</v>
@@ -985,7 +963,7 @@
     </row>
     <row r="3" spans="1:15" ht="17.25" thickBot="1">
       <c r="A3" s="17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9">
         <v>0</v>
@@ -1031,7 +1009,7 @@
     </row>
     <row r="4" spans="1:15" ht="17.25" thickBot="1">
       <c r="A4" s="17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9">
@@ -1060,22 +1038,22 @@
         <v>41167</v>
       </c>
       <c r="L4" s="9">
-        <v>21012</v>
+        <v>27012</v>
       </c>
       <c r="M4" s="10">
         <v>44986</v>
       </c>
       <c r="N4" s="10">
-        <v>17193</v>
+        <v>23193</v>
       </c>
       <c r="O4" s="7">
         <f t="shared" si="0"/>
-        <v>0.76391673303490515</v>
+        <v>0.70576966990586865</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="17.25" thickBot="1">
       <c r="A5" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9">
         <v>116967</v>
@@ -1117,7 +1095,7 @@
     </row>
     <row r="6" spans="1:15" ht="17.25" thickBot="1">
       <c r="A6" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="9">
         <v>72725</v>
@@ -1245,7 +1223,7 @@
     </row>
     <row r="9" spans="1:15" ht="17.25" thickBot="1">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5">
         <v>168561</v>
@@ -1515,13 +1493,13 @@
         <v>352953</v>
       </c>
       <c r="L14" s="5">
-        <v>232623</v>
+        <v>238623</v>
       </c>
       <c r="M14" s="5">
         <v>278909</v>
       </c>
       <c r="N14" s="5">
-        <v>306667</v>
+        <v>312667</v>
       </c>
     </row>
   </sheetData>
